--- a/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos crónicos de la piel</t>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,9</t>
+          <t>0,8; 7,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,88</t>
+          <t>0,97; 10,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 12,82</t>
+          <t>2,43; 11,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,61</t>
+          <t>1,47; 13,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,39</t>
+          <t>2,24; 7,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,14</t>
+          <t>2,38; 10,13</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,03</t>
+          <t>0,35; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,6</t>
+          <t>1,34; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,01</t>
+          <t>0,92; 2,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,76</t>
+          <t>1,86; 4,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,93</t>
+          <t>0,38; 1,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,9</t>
+          <t>0,3; 1,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,34</t>
+          <t>0,55; 2,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,67</t>
+          <t>2,0; 4,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,57</t>
+          <t>0,5; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,27</t>
+          <t>1,02; 2,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,14</t>
+          <t>0,91; 2,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,03</t>
+          <t>2,17; 4,18</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,34</t>
+          <t>1,33; 7,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,56</t>
+          <t>1,72; 7,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,48</t>
+          <t>1,07; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,59</t>
+          <t>0,96; 5,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,52</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,55</t>
+          <t>0,88; 3,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,28</t>
+          <t>0,9; 3,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,41</t>
+          <t>1,9; 5,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,68</t>
+          <t>1,73; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,18</t>
+          <t>0,78; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,83</t>
+          <t>2,34; 4,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,56</t>
+          <t>0,46; 1,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,22</t>
+          <t>0,81; 2,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,79</t>
+          <t>0,97; 2,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,53</t>
+          <t>2,29; 4,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,28</t>
+          <t>0,52; 1,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,61</t>
+          <t>1,41; 2,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,12</t>
+          <t>1,06; 2,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,23</t>
+          <t>2,56; 4,25</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2658</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7594</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>735; 6657</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>533; 5712</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2031; 9389</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4631</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>909; 8183</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4085</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3935; 13245</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4934</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2776; 11816</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8041</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14131</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16215</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8622</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14579</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>30346</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1452; 8897</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6036; 17171</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4356; 13622</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8538; 22557</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1814; 8631</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1458; 8527</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2709; 10837</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10317; 24163</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4501; 14021</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9638; 22671</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8785; 21674</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>21213; 40804</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5290</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6546</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10866</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4466</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2195; 11632</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4369</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2566; 11033</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3001</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4584</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2009; 10491</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1767; 10280</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4913</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2961; 11748</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3257; 12742</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6336; 17211</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18278</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9273</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>24771</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28751</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>47102</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10293</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12212; 26476</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5460; 15438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15551; 32197</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3293; 12023</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6055; 17236</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7258; 19103</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>17429; 34768</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7282; 18606</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>20544; 39130</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15338; 30510</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>36451; 60662</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,24</t>
+          <t>0,73; 6,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,27 +732,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,45</t>
+          <t>1,02; 10,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,24</t>
+          <t>2,53; 12,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,2</t>
+          <t>1,61; 14,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,55</t>
+          <t>2,28; 7,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,13</t>
+          <t>2,23; 9,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,14</t>
+          <t>0,37; 2,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,82</t>
+          <t>1,35; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,88</t>
+          <t>0,96; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,91</t>
+          <t>1,85; 4,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,81</t>
+          <t>0,38; 1,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,73</t>
+          <t>0,31; 1,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,22</t>
+          <t>0,56; 2,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,68</t>
+          <t>2,01; 4,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,57</t>
+          <t>0,52; 1,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,41</t>
+          <t>0,99; 2,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,26</t>
+          <t>0,94; 2,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,18</t>
+          <t>2,23; 4,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,03</t>
+          <t>1,39; 6,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,38</t>
+          <t>1,88; 7,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,6</t>
+          <t>1,3; 5,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,61</t>
+          <t>0,87; 5,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,18; 1,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,49</t>
+          <t>0,97; 3,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,54</t>
+          <t>0,87; 3,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,17</t>
+          <t>1,93; 5,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,51</t>
+          <t>0,38; 1,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,75</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,19</t>
+          <t>0,76; 2,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,85</t>
+          <t>2,22; 4,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,67</t>
+          <t>0,45; 1,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,31</t>
+          <t>0,81; 2,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,56</t>
+          <t>1,03; 2,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,56</t>
+          <t>2,25; 4,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,33</t>
+          <t>0,52; 1,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,69</t>
+          <t>1,48; 2,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,11</t>
+          <t>1,09; 2,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,25</t>
+          <t>2,58; 4,16</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>735; 6657</t>
+          <t>670; 6208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>533; 5712</t>
+          <t>560; 5537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 4747</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2031; 9389</t>
+          <t>2113; 10045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4631</t>
+          <t>0; 4924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>909; 8183</t>
+          <t>999; 9038</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4085</t>
+          <t>0; 4094</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3935; 13245</t>
+          <t>4005; 12554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4934</t>
+          <t>0; 4583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2776; 11816</t>
+          <t>2608; 11504</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1452; 8897</t>
+          <t>1545; 8340</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6036; 17171</t>
+          <t>6082; 17068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4356; 13622</t>
+          <t>4526; 13496</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8538; 22557</t>
+          <t>8505; 22357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1814; 8631</t>
+          <t>1805; 9156</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1458; 8527</t>
+          <t>1538; 8981</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2709; 10837</t>
+          <t>2734; 10842</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10317; 24163</t>
+          <t>10403; 25553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4501; 14021</t>
+          <t>4659; 14359</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9638; 22671</t>
+          <t>9296; 21662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8785; 21674</t>
+          <t>9078; 21229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21213; 40804</t>
+          <t>21802; 40987</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4466</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2195; 11632</t>
+          <t>2302; 10743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4369</t>
+          <t>0; 3968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2566; 11033</t>
+          <t>2813; 11415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3001</t>
+          <t>0; 3013</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4584</t>
+          <t>0; 4519</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2009; 10491</t>
+          <t>2429; 10859</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1767; 10280</t>
+          <t>1595; 10017</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4913</t>
+          <t>592; 5028</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2961; 11748</t>
+          <t>3267; 12343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3257; 12742</t>
+          <t>3136; 12081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6336; 17211</t>
+          <t>6441; 17298</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2517; 10293</t>
+          <t>2582; 10688</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12212; 26476</t>
+          <t>11700; 25770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5460; 15438</t>
+          <t>5346; 15234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15551; 32197</t>
+          <t>14732; 31055</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3293; 12023</t>
+          <t>3233; 11887</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6055; 17236</t>
+          <t>6086; 17513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7258; 19103</t>
+          <t>7657; 19954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17429; 34768</t>
+          <t>17113; 34309</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7282; 18606</t>
+          <t>7308; 18192</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20544; 39130</t>
+          <t>21579; 40147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15338; 30510</t>
+          <t>15728; 31162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36451; 60662</t>
+          <t>36811; 59312</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,04</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2,88; 12,82</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,02</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,7; 15,6</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 6,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,74; 6,9</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 10,13</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,47</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 12,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,18</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,58</t>
+          <t>1,21; 10,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,16</t>
+          <t>2,23; 7,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 9,86</t>
+          <t>2,42; 11,17</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,0</t>
+          <t>0,38; 1,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,8</t>
+          <t>0,31; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,86</t>
+          <t>0,68; 2,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,86</t>
+          <t>1,97; 4,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,92</t>
+          <t>0,33; 2,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,82</t>
+          <t>1,33; 3,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,22</t>
+          <t>0,98; 3,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,95</t>
+          <t>1,99; 5,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,61</t>
+          <t>0,52; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,3</t>
+          <t>0,94; 2,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,21</t>
+          <t>0,93; 2,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,2</t>
+          <t>2,34; 4,28</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,2%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,5</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>1,15; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,63</t>
+          <t>1,13; 6,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>1,35; 6,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,79</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,46</t>
+          <t>1,98; 7,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,51</t>
+          <t>0,18; 1,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,66</t>
+          <t>0,9; 3,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,35</t>
+          <t>0,86; 3,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,2</t>
+          <t>2,04; 5,86</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,43; 1,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>0,79; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,16</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,68</t>
+          <t>2,35; 4,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,65</t>
+          <t>0,31; 1,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,34</t>
+          <t>1,72; 3,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,68</t>
+          <t>0,75; 2,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,5</t>
+          <t>2,54; 5,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,3</t>
+          <t>0,52; 1,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,76</t>
+          <t>1,44; 2,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,15</t>
+          <t>1,09; 2,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,16</t>
+          <t>2,72; 4,47</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2658</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4936</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7594</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7594</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5943</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 4376</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2402; 10711</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4131</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>963; 8851</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>670; 6208</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>680; 6344</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>560; 5537</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4747</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2113; 10045</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4924</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>999; 9038</t>
+          <t>564; 5092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4094</t>
+          <t>0; 4531</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4005; 12554</t>
+          <t>3912; 12967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4583</t>
+          <t>0; 4577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2608; 11504</t>
+          <t>2500; 11564</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15170</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4120</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10330</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8041</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14131</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>29736</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1545; 8340</t>
+          <t>1821; 9220</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6082; 17068</t>
+          <t>1545; 9336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4526; 13496</t>
+          <t>3341; 11434</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8505; 22357</t>
+          <t>9362; 22452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1805; 9156</t>
+          <t>1393; 8430</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1538; 8981</t>
+          <t>5970; 16200</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2734; 10842</t>
+          <t>4642; 14239</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10403; 25553</t>
+          <t>8585; 22576</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4659; 14359</t>
+          <t>4656; 13993</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9296; 21662</t>
+          <t>8831; 21378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9078; 21229</t>
+          <t>8961; 20612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21802; 40987</t>
+          <t>21266; 38871</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1267</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5290</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1231</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11289</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2302; 10743</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3968</t>
+          <t>2149; 10273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2813; 11415</t>
+          <t>1911; 10382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3013</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>2228; 10487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2429; 10859</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1595; 10017</t>
+          <t>2971; 11901</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592; 5028</t>
+          <t>597; 5036</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3267; 12343</t>
+          <t>3023; 11954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3136; 12081</t>
+          <t>3096; 11799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6441; 17298</t>
+          <t>6498; 18671</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2582; 10688</t>
+          <t>3113; 11247</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11700; 25770</t>
+          <t>5902; 16615</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5346; 15234</t>
+          <t>7671; 20758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14732; 31055</t>
+          <t>16439; 33216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3233; 11887</t>
+          <t>2129; 10536</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6086; 17513</t>
+          <t>12126; 26014</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7657; 19954</t>
+          <t>5285; 15348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17113; 34309</t>
+          <t>15931; 33371</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7308; 18192</t>
+          <t>7244; 17940</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21579; 40147</t>
+          <t>21008; 38023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15728; 31162</t>
+          <t>15747; 30705</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36811; 59312</t>
+          <t>36206; 59389</t>
         </is>
       </c>
     </row>
